--- a/3.xlsx
+++ b/3.xlsx
@@ -1,37 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dyeing" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,21 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -79,44 +136,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -143,15 +200,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -178,7 +234,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -190,150 +245,234 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/3.xlsx
+++ b/3.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Dyeing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="finishing" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,4 +476,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/3.xlsx
+++ b/3.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Dyeing" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="finishing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="utilities department" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -532,4 +533,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/3.xlsx
+++ b/3.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,20 @@
           <t>ملاحظات</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,20 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pumps</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,6 +501,20 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Heat exchangers</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,20 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,6 +585,20 @@
           <t>ملاحظات</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dryers</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,6 +599,20 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rollers</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,6 +613,20 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Conveyors</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -639,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,6 +684,20 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Boilers</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/3.xlsx
+++ b/3.xlsx
@@ -639,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -698,6 +698,20 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Air compressors</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/3.xlsx
+++ b/3.xlsx
@@ -639,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,6 +712,20 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chillers</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/3.xlsx
+++ b/3.xlsx
@@ -639,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -726,6 +726,20 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Water treatment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/3.xlsx
+++ b/3.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +627,20 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Taining winding machine TN35</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Dyeing" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="finishing" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="utilities department" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="قطع_الغيار" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,4 +758,80 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>اسم القطعة</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المقاس</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الرصيد الموجود</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>مدة التوريد</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ضرورية</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>اسم الماكينة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>فلتر هوا</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Air compressors</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/3.xlsx
+++ b/3.xlsx
@@ -654,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,6 +696,16 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
         </is>
       </c>
     </row>
@@ -712,6 +722,8 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -726,6 +738,8 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -740,6 +754,8 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -754,6 +770,46 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Air compressors</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>تغير فلتر هوا</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>احمد</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>فلتر هوا (كمية 1)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -807,18 +863,14 @@
           <t>فلتر هوا</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
+      <c r="B2" t="n">
+        <v>222</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/3.xlsx
+++ b/3.xlsx
@@ -822,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,6 +883,36 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>فلتر زيت</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Air compressors</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/3.xlsx
+++ b/3.xlsx
@@ -822,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,27 +889,53 @@
           <t>فلتر زيت</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B3" t="n">
+        <v>4</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Air compressors</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>طرمبه</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Air compressors</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Chillers</t>
         </is>
       </c>
     </row>

--- a/3.xlsx
+++ b/3.xlsx
@@ -654,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,44 @@
       <c r="J6" t="inlineStr">
         <is>
           <t>فلتر هوا (كمية 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Air compressors</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>تغير فلتر الزيت</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>علي</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>فلتر زيت (كمية 1)</t>
         </is>
       </c>
     </row>
@@ -893,7 +931,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>21</v>
@@ -915,18 +953,14 @@
           <t>طرمبه</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="B4" t="n">
+        <v>8</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="D4" t="n">
+        <v>21</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>

--- a/3.xlsx
+++ b/3.xlsx
@@ -860,7 +860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,6 +973,36 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>رولمان بلي</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6006</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Chillers</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/3.xlsx
+++ b/3.xlsx
@@ -654,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,44 +808,6 @@
       <c r="J6" t="inlineStr">
         <is>
           <t>فلتر هوا (كمية 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Air compressors</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>صيانه</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>تغير فلتر الزيت</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>علي</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>فلتر زيت (كمية 1)</t>
         </is>
       </c>
     </row>
@@ -860,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,18 +941,14 @@
           <t>رولمان بلي</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>6006</t>
-        </is>
+      <c r="B5" t="n">
+        <v>6006</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D5" t="n">
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1000,6 +958,36 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Chillers</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>impeller</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>70*9*2</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pumps</t>
         </is>
       </c>
     </row>

--- a/3.xlsx
+++ b/3.xlsx
@@ -973,12 +973,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>

--- a/3.xlsx
+++ b/3.xlsx
@@ -822,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,34 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>impeller</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>70*9*2</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Pumps</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/3.xlsx
+++ b/3.xlsx
@@ -822,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,6 +961,36 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>impeller</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>70*9*2</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pumps</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/3.xlsx
+++ b/3.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,16 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
         </is>
       </c>
     </row>
@@ -488,6 +498,8 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -502,6 +514,8 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -516,6 +530,8 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -530,6 +546,46 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pumps</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>تغير</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>حماده</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>impeller (كمية 1)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -973,12 +1029,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>

--- a/3.xlsx
+++ b/3.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,6 +582,44 @@
         <v>0.6</v>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>impeller (كمية 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pumps</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>تغير</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>حماده</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>impeller (كمية 1)</t>
         </is>
@@ -1029,7 +1067,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>

--- a/3.xlsx
+++ b/3.xlsx
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +900,44 @@
         <v>0.5</v>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>فلتر هوا (كمية 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Air compressors</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>تغير</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>حماده</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>فلتر هوا (كمية 1)</t>
         </is>
@@ -961,7 +999,7 @@
         <v>222</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>21</v>

--- a/3.xlsx
+++ b/3.xlsx
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -940,6 +940,44 @@
       <c r="J7" t="inlineStr">
         <is>
           <t>فلتر هوا (كمية 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Air compressors</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>تغير</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>علي</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>فلتر زيت (كمية 1)</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1063,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>21</v>

--- a/3.xlsx
+++ b/3.xlsx
@@ -12,6 +12,7 @@
     <sheet name="finishing" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="utilities department" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="قطع_الغيار" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="صيانة_وقائية" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -50,8 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1162,4 +1167,86 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>نوع_الصيانة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>اسم_البند</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الفترة_بالأيام</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>آخر_تنفيذ</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>التاريخ_التالي</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>قطع_غيار_مستخدمة_افتراضية</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>يومية</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1-Check temperature &amp; pressure readings</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/3.xlsx
+++ b/3.xlsx
@@ -21,9 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -54,9 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1175,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1246,6 +1249,32 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>يومية</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1-Check temperature &amp; pressure readings </t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1269,11 +1269,37 @@
         <v>1</v>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>46126</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>يومية</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2_leakage (steam / water / chemicals)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1295,11 +1295,37 @@
         <v>1</v>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>46126</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>يومية</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_pump noise &amp; vibrationpump </t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,11 +1321,37 @@
         <v>1</v>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>46126</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>أسبوعية</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1_Inspect valves &amp; actuators</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,11 +1347,37 @@
         <v>7</v>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>46132</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>أسبوعية</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2-Clean filters &amp; strainers</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,11 +1373,37 @@
         <v>7</v>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>46132</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>أسبوعية</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3-Check safety valves</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1399,11 +1399,37 @@
         <v>7</v>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="1" t="n">
         <v>46132</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>شهرية</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1-Inspect heat exchanger efficiency</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1425,11 +1425,37 @@
         <v>30</v>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="1" t="n">
         <v>46155</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>شهرية</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2-Check motor alignment &amp; coupling</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1451,11 +1451,37 @@
         <v>30</v>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="1" t="n">
         <v>46155</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>سنوية</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1-Full shutdown inspection Replace seals, gaskets</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>365</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" s="2" t="n">
+        <v>46490</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,11 +1477,37 @@
         <v>365</v>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="1" t="n">
         <v>46490</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>سنوية</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2-Pressure vessel inspection (Safety critical)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>365</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" s="2" t="n">
+        <v>46490</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1503,11 +1503,37 @@
         <v>365</v>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="1" t="n">
         <v>46490</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Taining winding machine TN35</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>يومية</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1-Clean machine (dust / fibers)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -58,8 +58,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1528,7 +1528,9 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" s="2" t="n">
+        <v>46125</v>
+      </c>
       <c r="F13" s="2" t="n">
         <v>46126</v>
       </c>

--- a/3.xlsx
+++ b/3.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -58,8 +58,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1528,14 +1528,40 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="1" t="n">
         <v>46125</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="1" t="n">
         <v>46126</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Taining winding machine TN35</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>يومية</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2-Check yarn tension</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,11 +1557,37 @@
         <v>1</v>
       </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="1" t="n">
         <v>46126</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Taining winding machine TN35</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>يومية</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3-Visual inspection</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1583,11 +1583,37 @@
         <v>1</v>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="1" t="n">
         <v>46126</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Taining winding machine TN35</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>أسبوعية</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1-Lubricate bearings</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1609,11 +1609,37 @@
         <v>7</v>
       </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="1" t="n">
         <v>46132</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Taining winding machine TN35</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>أسبوعية</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2-Check belts &amp; pulleys</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1635,11 +1635,37 @@
         <v>7</v>
       </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="1" t="n">
         <v>46132</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Taining winding machine TN35</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>أسبوعية</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3-Inspect sensors (yarn break detection)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1661,11 +1661,37 @@
         <v>7</v>
       </c>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="1" t="n">
         <v>46132</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Taining winding machine TN35</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>شهرية</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1-Check motor performance</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1687,11 +1687,37 @@
         <v>30</v>
       </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="1" t="n">
         <v>46155</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Taining winding machine TN35</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>شهرية</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2-Inspect electrical panel</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>30</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1713,11 +1713,37 @@
         <v>30</v>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="1" t="n">
         <v>46155</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Taining winding machine TN35</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>سنوية</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1-Full overhaul</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>365</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" s="2" t="n">
+        <v>46490</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1178,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1739,11 +1739,37 @@
         <v>365</v>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="1" t="n">
         <v>46490</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Taining winding machine TN35</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>سنوية</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2-Replace critical wear parts</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>365</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" s="2" t="n">
+        <v>46490</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -21,11 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -56,10 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1000,7 +997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,6 +1161,36 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Pumps</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>proximity sensor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>22256</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sensors</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1792,7 @@
         <v>365</v>
       </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="1" t="n">
         <v>46490</v>
       </c>
       <c r="G22" t="inlineStr"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,21 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
         </is>
       </c>
     </row>
@@ -505,6 +520,9 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -521,6 +539,9 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -537,6 +558,9 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -553,6 +577,9 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,6 +618,9 @@
           <t>impeller (كمية 1)</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -627,6 +657,60 @@
       <c r="J7" t="inlineStr">
         <is>
           <t>impeller (كمية 1)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>تلف الحساس</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>تم استبدال</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>حسام</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>proximity sensor (كمية 1)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>كهربائي</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ملتزم جزئياً</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1260,10 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
         <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>

--- a/3.xlsx
+++ b/3.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,6 +711,53 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>ملتزم جزئياً</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>خلل ف قرايه</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>تم العيار</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>حسام</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>كهربائي</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
         </is>
       </c>
     </row>
